--- a/tools/importer/reports/import-careers.report.xlsx
+++ b/tools/importer/reports/import-careers.report.xlsx
@@ -58,7 +58,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-26T11:37:36.705Z</t>
+    <t>2026-10-27T06:00:59.573Z</t>
   </si>
   <si>
     <t>Careers | JSW Motors</t>

--- a/tools/importer/reports/import-careers.report.xlsx
+++ b/tools/importer/reports/import-careers.report.xlsx
@@ -46,7 +46,7 @@
     <t>careers.report.json</t>
   </si>
   <si>
-    <t>["job-board"]</t>
+    <t>["careers-hero","job-board","careers-perks"]</t>
   </si>
   <si>
     <t>careers</t>
@@ -58,7 +58,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-27T06:00:59.573Z</t>
+    <t>2026-10-27T07:08:56.205Z</t>
   </si>
   <si>
     <t>Careers | JSW Motors</t>

--- a/tools/importer/reports/import-careers.report.xlsx
+++ b/tools/importer/reports/import-careers.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="78">
   <si>
     <t>_reportFile</t>
   </si>
@@ -58,7 +58,7 @@
     <t>success</t>
   </si>
   <si>
-    <t>2026-10-27T07:08:56.205Z</t>
+    <t>2026-10-27T12:21:36.632Z</t>
   </si>
   <si>
     <t>Careers | JSW Motors</t>
@@ -134,6 +134,24 @@
   </si>
   <si>
     <t>MG Latest Luxury &amp; Electric Cars in India - Prices &amp; Models</t>
+  </si>
+  <si>
+    <t>jsw-footer.report.json</t>
+  </si>
+  <si>
+    <t>["jsw-footer","jsw-footer-links","jsw-footer-social"]</t>
+  </si>
+  <si>
+    <t>jsw-footer</t>
+  </si>
+  <si>
+    <t>2026-10-27T12:21:28.409Z</t>
+  </si>
+  <si>
+    <t>JSW Footer</t>
+  </si>
+  <si>
+    <t>http://localhost:3000/drafts/jsw-footer/source.html</t>
   </si>
   <si>
     <t>jsw-nav.report.json</t>
@@ -615,7 +633,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -825,10 +843,10 @@
         <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
@@ -860,25 +878,25 @@
         <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8">
-        <v>6</v>
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>13</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="I8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
         <v>13</v>
@@ -886,31 +904,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
+      <c r="D9">
+        <v>6</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="J9" t="s">
         <v>13</v>
@@ -921,10 +939,10 @@
         <v>55</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>13</v>
@@ -933,27 +951,27 @@
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J10" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>62</v>
@@ -965,7 +983,7 @@
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G11" t="s">
         <v>63</v>
@@ -977,7 +995,7 @@
         <v>65</v>
       </c>
       <c r="J11" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1009,6 +1027,38 @@
         <v>71</v>
       </c>
       <c r="J12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+      <c r="G13" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s">
         <v>13</v>
       </c>
     </row>
